--- a/group_15_gantt chart.xlsx
+++ b/group_15_gantt chart.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91836\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6989f0f200046ae2/Desktop/SE-A-Mini-Project-1B-2025-26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7146234B-8516-465D-9292-8EA1BA26C775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{7146234B-8516-465D-9292-8EA1BA26C775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75350109-B23F-477B-958C-94F9C1FA8110}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,9 +142,6 @@
     <t>Database Design</t>
   </si>
   <si>
-    <t xml:space="preserve">Yash Shinde and Swati Vishwakarma </t>
-  </si>
-  <si>
     <t>Database Connectivity of all modules</t>
   </si>
   <si>
@@ -170,6 +167,9 @@
   </si>
   <si>
     <t xml:space="preserve">GANTT CHART </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QAll </t>
   </si>
 </sst>
 </file>
@@ -960,10 +960,48 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -971,46 +1009,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1378,42 +1378,42 @@
     </row>
     <row r="2" spans="1:68" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
+      <c r="B2" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
       <c r="H2" s="10"/>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="70" t="s">
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71"/>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="86"/>
+      <c r="S2" s="86"/>
+      <c r="T2" s="86"/>
+      <c r="U2" s="86"/>
+      <c r="V2" s="86"/>
+      <c r="W2" s="86"/>
+      <c r="X2" s="86"/>
+      <c r="Y2" s="86"/>
+      <c r="Z2" s="86"/>
+      <c r="AA2" s="86"/>
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="86"/>
+      <c r="AD2" s="86"/>
+      <c r="AE2" s="86"/>
       <c r="AF2" s="11"/>
       <c r="AG2" s="11"/>
       <c r="AH2" s="11"/>
@@ -1524,29 +1524,29 @@
     </row>
     <row r="4" spans="1:68" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="75" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
+      <c r="B4" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="73" t="s">
+      <c r="I4" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="92"/>
+      <c r="T4" s="92"/>
       <c r="U4" s="17" t="s">
         <v>3</v>
       </c>
@@ -1600,40 +1600,40 @@
     </row>
     <row r="5" spans="1:68" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A5" s="1"/>
-      <c r="B5" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
+      <c r="B5" s="87" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="75" t="s">
+      <c r="I5" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="77" t="s">
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="84"/>
+      <c r="U5" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="74"/>
-      <c r="AB5" s="74"/>
-      <c r="AC5" s="74"/>
+      <c r="V5" s="92"/>
+      <c r="W5" s="92"/>
+      <c r="X5" s="92"/>
+      <c r="Y5" s="92"/>
+      <c r="Z5" s="92"/>
+      <c r="AA5" s="92"/>
+      <c r="AB5" s="92"/>
+      <c r="AC5" s="92"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1816,195 +1816,195 @@
     </row>
     <row r="8" spans="1:68" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23"/>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="78" t="s">
+      <c r="C8" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="78" t="s">
+      <c r="D8" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="78" t="s">
+      <c r="H8" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="89" t="s">
+      <c r="I8" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="87"/>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="87"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="87"/>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87"/>
-      <c r="AB8" s="87"/>
-      <c r="AC8" s="87"/>
-      <c r="AD8" s="87"/>
-      <c r="AE8" s="87"/>
-      <c r="AF8" s="87"/>
-      <c r="AG8" s="87"/>
-      <c r="AH8" s="87"/>
-      <c r="AI8" s="87"/>
-      <c r="AJ8" s="87"/>
-      <c r="AK8" s="87"/>
-      <c r="AL8" s="87"/>
-      <c r="AM8" s="87"/>
-      <c r="AN8" s="87"/>
-      <c r="AO8" s="87"/>
-      <c r="AP8" s="87"/>
-      <c r="AQ8" s="87"/>
-      <c r="AR8" s="86" t="s">
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="75"/>
+      <c r="R8" s="75"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="75"/>
+      <c r="V8" s="75"/>
+      <c r="W8" s="75"/>
+      <c r="X8" s="75"/>
+      <c r="Y8" s="75"/>
+      <c r="Z8" s="75"/>
+      <c r="AA8" s="75"/>
+      <c r="AB8" s="75"/>
+      <c r="AC8" s="75"/>
+      <c r="AD8" s="75"/>
+      <c r="AE8" s="75"/>
+      <c r="AF8" s="75"/>
+      <c r="AG8" s="75"/>
+      <c r="AH8" s="75"/>
+      <c r="AI8" s="75"/>
+      <c r="AJ8" s="75"/>
+      <c r="AK8" s="75"/>
+      <c r="AL8" s="75"/>
+      <c r="AM8" s="75"/>
+      <c r="AN8" s="75"/>
+      <c r="AO8" s="75"/>
+      <c r="AP8" s="75"/>
+      <c r="AQ8" s="75"/>
+      <c r="AR8" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AS8" s="87"/>
-      <c r="AT8" s="87"/>
-      <c r="AU8" s="87"/>
-      <c r="AV8" s="87"/>
-      <c r="AW8" s="87"/>
-      <c r="AX8" s="87"/>
-      <c r="AY8" s="87"/>
-      <c r="AZ8" s="87"/>
-      <c r="BA8" s="87"/>
-      <c r="BB8" s="87"/>
-      <c r="BC8" s="87"/>
-      <c r="BD8" s="87"/>
-      <c r="BE8" s="87"/>
-      <c r="BF8" s="87"/>
-      <c r="BG8" s="87"/>
-      <c r="BH8" s="87"/>
-      <c r="BI8" s="87"/>
-      <c r="BJ8" s="87"/>
-      <c r="BK8" s="87"/>
-      <c r="BL8" s="87"/>
-      <c r="BM8" s="87"/>
-      <c r="BN8" s="87"/>
-      <c r="BO8" s="87"/>
-      <c r="BP8" s="87"/>
+      <c r="AS8" s="75"/>
+      <c r="AT8" s="75"/>
+      <c r="AU8" s="75"/>
+      <c r="AV8" s="75"/>
+      <c r="AW8" s="75"/>
+      <c r="AX8" s="75"/>
+      <c r="AY8" s="75"/>
+      <c r="AZ8" s="75"/>
+      <c r="BA8" s="75"/>
+      <c r="BB8" s="75"/>
+      <c r="BC8" s="75"/>
+      <c r="BD8" s="75"/>
+      <c r="BE8" s="75"/>
+      <c r="BF8" s="75"/>
+      <c r="BG8" s="75"/>
+      <c r="BH8" s="75"/>
+      <c r="BI8" s="75"/>
+      <c r="BJ8" s="75"/>
+      <c r="BK8" s="75"/>
+      <c r="BL8" s="75"/>
+      <c r="BM8" s="75"/>
+      <c r="BN8" s="75"/>
+      <c r="BO8" s="75"/>
+      <c r="BP8" s="75"/>
     </row>
     <row r="9" spans="1:68" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="88" t="s">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="88" t="s">
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="88" t="s">
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="T9" s="83"/>
-      <c r="U9" s="83"/>
-      <c r="V9" s="83"/>
-      <c r="W9" s="84"/>
-      <c r="X9" s="90" t="s">
+      <c r="T9" s="72"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="Y9" s="91"/>
-      <c r="Z9" s="91"/>
-      <c r="AA9" s="91"/>
-      <c r="AB9" s="92"/>
-      <c r="AC9" s="90" t="s">
+      <c r="Y9" s="80"/>
+      <c r="Z9" s="80"/>
+      <c r="AA9" s="80"/>
+      <c r="AB9" s="81"/>
+      <c r="AC9" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="AD9" s="91"/>
-      <c r="AE9" s="91"/>
-      <c r="AF9" s="91"/>
-      <c r="AG9" s="92"/>
-      <c r="AH9" s="90" t="s">
+      <c r="AD9" s="80"/>
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="80"/>
+      <c r="AG9" s="81"/>
+      <c r="AH9" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="AI9" s="91"/>
-      <c r="AJ9" s="91"/>
-      <c r="AK9" s="91"/>
-      <c r="AL9" s="92"/>
-      <c r="AM9" s="90" t="s">
+      <c r="AI9" s="80"/>
+      <c r="AJ9" s="80"/>
+      <c r="AK9" s="80"/>
+      <c r="AL9" s="81"/>
+      <c r="AM9" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="AN9" s="91"/>
-      <c r="AO9" s="91"/>
-      <c r="AP9" s="91"/>
-      <c r="AQ9" s="92"/>
-      <c r="AR9" s="85" t="s">
+      <c r="AN9" s="80"/>
+      <c r="AO9" s="80"/>
+      <c r="AP9" s="80"/>
+      <c r="AQ9" s="81"/>
+      <c r="AR9" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="AS9" s="83"/>
-      <c r="AT9" s="83"/>
-      <c r="AU9" s="83"/>
-      <c r="AV9" s="84"/>
-      <c r="AW9" s="85" t="s">
+      <c r="AS9" s="72"/>
+      <c r="AT9" s="72"/>
+      <c r="AU9" s="72"/>
+      <c r="AV9" s="73"/>
+      <c r="AW9" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="AX9" s="83"/>
-      <c r="AY9" s="83"/>
-      <c r="AZ9" s="83"/>
-      <c r="BA9" s="84"/>
-      <c r="BB9" s="85" t="s">
+      <c r="AX9" s="72"/>
+      <c r="AY9" s="72"/>
+      <c r="AZ9" s="72"/>
+      <c r="BA9" s="73"/>
+      <c r="BB9" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="BC9" s="83"/>
-      <c r="BD9" s="83"/>
-      <c r="BE9" s="83"/>
-      <c r="BF9" s="84"/>
-      <c r="BG9" s="85" t="s">
+      <c r="BC9" s="72"/>
+      <c r="BD9" s="72"/>
+      <c r="BE9" s="72"/>
+      <c r="BF9" s="73"/>
+      <c r="BG9" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="BH9" s="83"/>
-      <c r="BI9" s="83"/>
-      <c r="BJ9" s="83"/>
-      <c r="BK9" s="84"/>
-      <c r="BL9" s="85" t="s">
+      <c r="BH9" s="72"/>
+      <c r="BI9" s="72"/>
+      <c r="BJ9" s="72"/>
+      <c r="BK9" s="73"/>
+      <c r="BL9" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="BM9" s="83"/>
-      <c r="BN9" s="83"/>
-      <c r="BO9" s="83"/>
-      <c r="BP9" s="84"/>
+      <c r="BM9" s="72"/>
+      <c r="BN9" s="72"/>
+      <c r="BO9" s="72"/>
+      <c r="BP9" s="73"/>
     </row>
     <row r="10" spans="1:68" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
       <c r="I10" s="26" t="s">
         <v>27</v>
       </c>
@@ -2372,11 +2372,11 @@
       <c r="K13" s="47"/>
       <c r="L13" s="47"/>
       <c r="M13" s="47"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="93"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="70"/>
       <c r="S13" s="48"/>
       <c r="T13" s="48"/>
       <c r="U13" s="48"/>
@@ -2521,7 +2521,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" s="38">
         <v>46056</v>
@@ -2763,7 +2763,7 @@
         <v>39</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E18" s="38">
         <v>46077</v>
@@ -2844,10 +2844,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="38">
         <v>46091</v>
@@ -2928,10 +2928,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="38">
         <v>46098</v>
@@ -3012,7 +3012,7 @@
         <v>2.4</v>
       </c>
       <c r="C21" s="54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="37" t="s">
         <v>33</v>
@@ -3240,6 +3240,19 @@
     <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="O2:AE2"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="I4:T4"/>
+    <mergeCell ref="I5:T5"/>
+    <mergeCell ref="U5:AC5"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B5:G5"/>
     <mergeCell ref="BG9:BK9"/>
     <mergeCell ref="BL9:BP9"/>
     <mergeCell ref="AR8:BP8"/>
@@ -3256,19 +3269,6 @@
     <mergeCell ref="AR9:AV9"/>
     <mergeCell ref="AM9:AQ9"/>
     <mergeCell ref="BB9:BF9"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="O2:AE2"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="I4:T4"/>
-    <mergeCell ref="I5:T5"/>
-    <mergeCell ref="U5:AC5"/>
   </mergeCells>
   <conditionalFormatting sqref="H12:H16 H18:H21">
     <cfRule type="colorScale" priority="1">
